--- a/output/hospitals_data_hospitals_hospitals_in_aligarh.xlsx
+++ b/output/hospitals_data_hospitals_hospitals_in_aligarh.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,44 +453,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dr Ankur Varshneya</t>
+          <t>K K Hospital</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>088820 52769</t>
+          <t>090842 63669</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>drankururologist.com</t>
+          <t>kkich.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sewa Medical Services, Ramghat Rd, opposite Meenakshi Cinema, Sudhama Puri, Aligarh, Uttar Pradesh 202001</t>
+          <t>V3WR+GG5, Ramghat Rd, Avas Vikas Colony, Sumit Sarovar Colony, ADA Colony, Aligarh, Uttar Pradesh 202001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K K Hospital</t>
+          <t>Rawat Hospital</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>090842 63669</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>kkich.com</t>
-        </is>
-      </c>
+          <t>093190 52530</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>V3WR+GG5, Ramghat Rd, Avas Vikas Colony, Sumit Sarovar Colony, ADA Colony, Aligarh, Uttar Pradesh 202001</t>
+          <t>3, Agra Rd, near Canara Bank, Avas Vikas Colony, Sasni Gate, Aligarh, Uttar Pradesh 202001</t>
         </is>
       </c>
     </row>
@@ -519,36 +515,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maxfort Multispeciality Hospital</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>098370 40699</t>
-        </is>
-      </c>
+          <t>Ranjana hospital</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Indraprasth Enclave, Maxfort Multi-Speciality Hospital, Ramghat Rd, Kishanpur, Aligarh, Uttar Pradesh 202001</t>
+          <t>Pala Rd, near suhag guest house, Krishna Vihar, Gopal Puri, Aligarh, Uttar Pradesh 202001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rawat Hospital</t>
+          <t>Maxfort Multispeciality Hospital</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>093190 52530</t>
+          <t>098370 40699</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3, Avas Vikas Colony, Agra Rd, Near Canara Bank, Sasni Gate, Aligarh, Uttar Pradesh 202001</t>
+          <t>Indraprasth Enclave, Maxfort Multi-Speciality Hospital, Ramghat Rd, Kishanpur, Aligarh, Uttar Pradesh 202001</t>
         </is>
       </c>
     </row>
